--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5332,7 +5332,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -5389,7 +5389,7 @@
       <c r="N97" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr"/>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
       <c r="C98" s="9" t="inlineStr"/>
       <c r="D98" s="9" t="inlineStr">
         <is>
@@ -5419,7 +5423,11 @@
         </is>
       </c>
       <c r="M98" s="9" t="inlineStr"/>
-      <c r="N98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
@@ -5430,7 +5438,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -5487,7 +5495,7 @@
       <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5505,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr"/>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
       <c r="C100" s="9" t="inlineStr"/>
       <c r="D100" s="9" t="inlineStr"/>
       <c r="E100" s="9" t="inlineStr"/>
@@ -5509,7 +5521,11 @@
       <c r="K100" s="9" t="inlineStr"/>
       <c r="L100" s="9" t="inlineStr"/>
       <c r="M100" s="9" t="inlineStr"/>
-      <c r="N100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
@@ -5526,13 +5542,13 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -5598,8 +5614,16 @@
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr"/>
-      <c r="C102" s="9" t="inlineStr"/>
-      <c r="D102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>LWin</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>LAlt</t>
+        </is>
+      </c>
       <c r="E102" s="9" t="inlineStr"/>
       <c r="F102" s="9" t="inlineStr"/>
       <c r="G102" s="9" t="inlineStr"/>
@@ -5730,7 +5754,7 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -5787,7 +5811,7 @@
       <c r="N106" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5821,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr"/>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
           <t>🖱右</t>
@@ -5825,7 +5853,11 @@
           <t>🖱右</t>
         </is>
       </c>
-      <c r="N107" s="9" t="inlineStr"/>
+      <c r="N107" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -5836,7 +5868,7 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -5893,7 +5925,7 @@
       <c r="N108" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5935,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr"/>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
           <t>🖱進</t>
@@ -5931,7 +5967,11 @@
           <t>🖱進</t>
         </is>
       </c>
-      <c r="N109" s="9" t="inlineStr"/>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -5948,13 +5988,13 @@
       <c r="C110" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -6020,8 +6060,16 @@
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr"/>
-      <c r="C111" s="9" t="inlineStr"/>
-      <c r="D111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>LWin</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>LAlt</t>
+        </is>
+      </c>
       <c r="E111" s="9" t="inlineStr"/>
       <c r="F111" s="9" t="inlineStr"/>
       <c r="G111" s="9" t="inlineStr"/>
@@ -10902,7 +10950,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -10959,7 +11007,7 @@
       <c r="N97" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -10969,7 +11017,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr"/>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
       <c r="C98" s="9" t="inlineStr"/>
       <c r="D98" s="9" t="inlineStr">
         <is>
@@ -10989,7 +11041,11 @@
         </is>
       </c>
       <c r="M98" s="9" t="inlineStr"/>
-      <c r="N98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
@@ -11000,7 +11056,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -11057,7 +11113,7 @@
       <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11123,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr"/>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
       <c r="C100" s="9" t="inlineStr"/>
       <c r="D100" s="9" t="inlineStr"/>
       <c r="E100" s="9" t="inlineStr"/>
@@ -11079,7 +11139,11 @@
       <c r="K100" s="9" t="inlineStr"/>
       <c r="L100" s="9" t="inlineStr"/>
       <c r="M100" s="9" t="inlineStr"/>
-      <c r="N100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
@@ -11096,13 +11160,13 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -11168,8 +11232,16 @@
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr"/>
-      <c r="C102" s="9" t="inlineStr"/>
-      <c r="D102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_WIN</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_ALT</t>
+        </is>
+      </c>
       <c r="E102" s="9" t="inlineStr"/>
       <c r="F102" s="9" t="inlineStr"/>
       <c r="G102" s="9" t="inlineStr"/>
@@ -11300,7 +11372,7 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -11357,7 +11429,7 @@
       <c r="N106" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11439,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr"/>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB2</t>
@@ -11395,7 +11471,11 @@
           <t>&amp;mkp MB2</t>
         </is>
       </c>
-      <c r="N107" s="9" t="inlineStr"/>
+      <c r="N107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -11406,7 +11486,7 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -11463,7 +11543,7 @@
       <c r="N108" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -11473,7 +11553,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr"/>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB5</t>
@@ -11501,7 +11585,11 @@
           <t>&amp;mkp MB5</t>
         </is>
       </c>
-      <c r="N109" s="9" t="inlineStr"/>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -11518,13 +11606,13 @@
       <c r="C110" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -11590,8 +11678,16 @@
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr"/>
-      <c r="C111" s="9" t="inlineStr"/>
-      <c r="D111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_WIN</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_ALT</t>
+        </is>
+      </c>
       <c r="E111" s="9" t="inlineStr"/>
       <c r="F111" s="9" t="inlineStr"/>
       <c r="G111" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5332,7 +5332,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp LCTRL</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -5389,7 +5389,7 @@
       <c r="N97" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;kp RCTRL</t>
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>LCtrl</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr"/>
@@ -5425,7 +5425,7 @@
       <c r="M98" s="9" t="inlineStr"/>
       <c r="N98" s="9" t="inlineStr">
         <is>
-          <t>RCtrl</t>
+          <t>▽</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;kp LEFT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -5495,7 +5495,7 @@
       <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;kp RIGHT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>LShift</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr"/>
@@ -5523,7 +5523,7 @@
       <c r="M100" s="9" t="inlineStr"/>
       <c r="N100" s="9" t="inlineStr">
         <is>
-          <t>RShift</t>
+          <t>▽</t>
         </is>
       </c>
     </row>
@@ -5542,13 +5542,13 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;kp LEFT_WIN</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;kp LEFT_ALT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -5616,12 +5616,12 @@
       <c r="B102" s="9" t="inlineStr"/>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>LWin</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>LAlt</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr"/>
@@ -10950,7 +10950,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp LCTRL</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -11007,7 +11007,7 @@
       <c r="N97" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;kp RCTRL</t>
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LCTRL</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr"/>
@@ -11043,7 +11043,7 @@
       <c r="M98" s="9" t="inlineStr"/>
       <c r="N98" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp RCTRL</t>
+          <t>▽</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;kp LEFT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -11113,7 +11113,7 @@
       <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;kp RIGHT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_SHIFT</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr"/>
@@ -11141,7 +11141,7 @@
       <c r="M100" s="9" t="inlineStr"/>
       <c r="N100" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
+          <t>▽</t>
         </is>
       </c>
     </row>
@@ -11160,13 +11160,13 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;kp LEFT_WIN</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;kp LEFT_ALT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -11234,12 +11234,12 @@
       <c r="B102" s="9" t="inlineStr"/>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_WIN</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_ALT</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -4500,7 +4500,7 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp CAPSLOCK</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -4512,19 +4512,19 @@
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -4557,7 +4557,7 @@
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -4567,15 +4567,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr"/>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>CAPSLOCK</t>
+        </is>
+      </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
           <t>リセット</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
@@ -4587,7 +4603,11 @@
           <t>リセット</t>
         </is>
       </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -4598,7 +4618,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -4610,7 +4630,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -4655,7 +4675,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -4665,9 +4685,17 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
       <c r="F82" s="9" t="inlineStr">
         <is>
@@ -4685,7 +4713,11 @@
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -10118,7 +10150,7 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp CAPSLOCK</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -10130,19 +10162,19 @@
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -10175,7 +10207,7 @@
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -10185,15 +10217,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr"/>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp CAPSLOCK</t>
+        </is>
+      </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
@@ -10205,7 +10253,11 @@
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -10216,7 +10268,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -10228,7 +10280,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -10273,7 +10325,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -10283,9 +10335,17 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
       <c r="F82" s="9" t="inlineStr">
         <is>
@@ -10303,7 +10363,11 @@
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -4500,13 +4500,13 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp CAPSLOCK</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4551,7 +4551,7 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
@@ -4567,16 +4567,8 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>CAPSLOCK</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
       <c r="D80" s="9" t="inlineStr">
         <is>
           <t>PRINTSCREEN</t>
@@ -4598,11 +4590,7 @@
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
+      <c r="M80" s="9" t="inlineStr"/>
       <c r="N80" s="9" t="inlineStr">
         <is>
           <t>F11</t>
@@ -4642,7 +4630,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr"/>
@@ -4651,7 +4639,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -4697,19 +4685,11 @@
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
@@ -10150,13 +10130,13 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp CAPSLOCK</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -10201,7 +10181,7 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
@@ -10217,16 +10197,8 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp CAPSLOCK</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
       <c r="D80" s="9" t="inlineStr">
         <is>
           <t>&amp;kp PRINTSCREEN</t>
@@ -10248,11 +10220,7 @@
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
+      <c r="M80" s="9" t="inlineStr"/>
       <c r="N80" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F11</t>
@@ -10292,7 +10260,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr"/>
@@ -10301,7 +10269,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -10347,19 +10315,11 @@
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -4506,25 +4506,25 @@
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -4551,13 +4551,13 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -4568,26 +4568,34 @@
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr"/>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -4598,7 +4606,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -4610,7 +4618,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -4622,7 +4630,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr"/>
@@ -4631,7 +4639,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -4655,7 +4663,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -4665,27 +4673,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -10124,25 +10136,25 @@
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -10169,13 +10181,13 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -10186,26 +10198,34 @@
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr"/>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -10216,7 +10236,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -10228,7 +10248,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -10240,7 +10260,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr"/>
@@ -10249,7 +10269,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -10273,7 +10293,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -10283,27 +10303,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
